--- a/output/top_customers.xlsx
+++ b/output/top_customers.xlsx
@@ -443,7 +443,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>455</v>
+        <v>520.5</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/output/top_customers.xlsx
+++ b/output/top_customers.xlsx
@@ -495,7 +495,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
